--- a/evaluations/LLAMA3.2_Evaluation/Rodier-Finding-Questions.xlsx
+++ b/evaluations/LLAMA3.2_Evaluation/Rodier-Finding-Questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Science UWA\Capstone\Capstone-Project-Evaluation\evaluations\LLAMA3.2_Evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72AE8AB4-1A08-49D4-A53E-A01491C1C470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DBF392-7205-4424-9A68-0FEEB3302A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{14E450A7-3B53-409C-AA63-99E7691AB703}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{14E450A7-3B53-409C-AA63-99E7691AB703}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>document</t>
   </si>
@@ -132,13 +132,19 @@
   </si>
   <si>
     <t xml:space="preserve">Not applicable in this case; the death occurred during a recreational activity at sea, not under institutional supervision or care </t>
+  </si>
+  <si>
+    <t>Yes. The Rodier case underscores a broader public safety lesson about the persistent dangers of rock fishing and the need for preventive measures at hazardous coastal sites. The coroner observed that while Western Australia has since introduced safety improvements such as life rings and tether points at popular rock fishing locations, remote areas like Quobba Station remain perilous and largely unmonitored. The finding highlights how environmental risks, rather than institutional failures, were central, emphasizing the importance of sustained public education, signage, and infrastructure to reduce fatalities from recreational fishing accidents</t>
+  </si>
+  <si>
+    <t>Does this case highlight any broader patterns or lessons relevant to public safety or institutional care?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +157,12 @@
       <color theme="1"/>
       <name val="Cambria"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -173,10 +185,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF4AAA93-B83E-48F1-9311-6D4109DFC4F7}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
@@ -684,7 +699,19 @@
         <v>31</v>
       </c>
     </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>